--- a/docs/data/beidan_26083_dashboard.xlsx
+++ b/docs/data/beidan_26083_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26083期 比赛看板（皇冠历史相同亚盘） — 2026-08-07</t>
+          <t>⚽ 北京单场26083期 比赛看板（皇冠历史相同亚盘） — 2026-08-08</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -980,10 +1004,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -1036,10 +1064,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -1092,10 +1124,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1204,10 +1244,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1260,10 +1304,14 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -1316,10 +1364,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1372,24 +1424,32 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr">
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>38%</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>29%</t>
         </is>
       </c>
     </row>
@@ -1424,10 +1484,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1480,10 +1544,14 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1536,10 +1604,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1592,10 +1664,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1648,10 +1724,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -1704,10 +1784,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1760,10 +1844,14 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -1816,10 +1904,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1872,10 +1964,14 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1928,10 +2024,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1984,10 +2084,14 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -2040,10 +2144,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2096,10 +2204,14 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -2152,10 +2264,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2208,10 +2324,14 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -2264,10 +2384,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2320,10 +2444,14 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2376,10 +2504,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2432,10 +2564,14 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2488,10 +2624,14 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -2544,10 +2684,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2600,10 +2744,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -2656,10 +2804,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -2712,10 +2864,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2768,10 +2924,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -2804,7 +2964,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>08-08 02:45</t>
+          <t>08-08 03:15</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2824,10 +2984,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2880,10 +3044,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -2936,10 +3104,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2992,10 +3164,14 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3048,10 +3224,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3104,10 +3284,14 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -3160,10 +3344,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3196,7 +3384,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>08-08 06:30</t>
+          <t>08-08 06:35</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3216,10 +3404,14 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3272,10 +3464,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3328,10 +3524,14 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -3384,10 +3584,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -3440,10 +3644,14 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3496,10 +3704,14 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3556,20 +3768,24 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>42%</t>
         </is>
       </c>
     </row>
@@ -3944,20 +4160,24 @@
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>34%</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>37%</t>
         </is>
       </c>
     </row>
@@ -4052,20 +4272,24 @@
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>40%</t>
         </is>
       </c>
     </row>
@@ -4104,20 +4328,24 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
           <t>34%</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>37%</t>
         </is>
       </c>
     </row>
@@ -4604,20 +4832,24 @@
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>受半球/一球</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -8968,20 +9200,24 @@
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr"/>
-      <c r="I153" s="5" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>受半球/一球</t>
+        </is>
+      </c>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="L153" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -10924,20 +11160,24 @@
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
-      <c r="I188" s="4" t="inlineStr"/>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>42%</t>
         </is>
       </c>
     </row>
@@ -12036,20 +12276,24 @@
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
-      <c r="I208" s="4" t="inlineStr"/>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>球半/两球</t>
+        </is>
+      </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>32%</t>
         </is>
       </c>
     </row>
@@ -13376,20 +13620,24 @@
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
-      <c r="I232" s="4" t="inlineStr"/>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="K232" s="4" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>37%</t>
         </is>
       </c>
     </row>
@@ -13428,20 +13676,24 @@
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr"/>
-      <c r="I233" s="5" t="inlineStr"/>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
       <c r="J233" s="6" t="inlineStr">
         <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="K233" s="5" t="inlineStr">
-        <is>
-          <t>31%</t>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="K233" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
         </is>
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>12%</t>
         </is>
       </c>
     </row>
@@ -14488,20 +14740,24 @@
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
-      <c r="I252" s="4" t="inlineStr"/>
+      <c r="I252" s="4" t="inlineStr">
+        <is>
+          <t>受半球/一球</t>
+        </is>
+      </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="K252" s="4" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14828,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>08-10 02:00</t>
+          <t>08-10 02:15</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">

--- a/docs/data/beidan_26083_dashboard.xlsx
+++ b/docs/data/beidan_26083_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26083期 比赛看板（皇冠历史相同亚盘） — 2026-08-08</t>
+          <t>⚽ 北京单场26083期 比赛看板（皇冠历史相同亚盘） — 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -3764,10 +3764,14 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3820,10 +3824,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3876,10 +3884,14 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3932,10 +3944,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr"/>
+          <t>1:5</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3988,10 +4004,14 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4044,10 +4064,14 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4100,10 +4124,14 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4156,10 +4184,14 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4212,10 +4244,14 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4268,10 +4304,14 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -4324,10 +4364,14 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4380,10 +4424,14 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4436,10 +4484,14 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -4492,10 +4544,14 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4548,10 +4604,14 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4604,10 +4664,14 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4660,10 +4724,14 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4716,10 +4784,14 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4772,10 +4844,14 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4828,10 +4904,14 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -4884,10 +4964,14 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4940,10 +5024,14 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr"/>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -4996,10 +5084,14 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5052,10 +5144,14 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5108,10 +5204,14 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr"/>
+          <t>1:6</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5164,10 +5264,14 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5220,10 +5324,14 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5276,10 +5384,14 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5332,10 +5444,14 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -5388,10 +5504,14 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5444,10 +5564,14 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5500,10 +5624,14 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5556,10 +5684,14 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -5612,10 +5744,14 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5668,10 +5804,14 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5724,10 +5864,14 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5780,10 +5924,14 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5836,10 +5984,14 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5892,10 +6044,14 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -5948,10 +6104,14 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6004,10 +6164,14 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6060,10 +6224,14 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -6116,10 +6284,14 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6172,10 +6344,14 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -6228,10 +6404,14 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6284,10 +6464,14 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6340,10 +6524,14 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6396,10 +6584,14 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -6452,10 +6644,14 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6508,10 +6704,14 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -6564,10 +6764,14 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6620,10 +6824,14 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -6676,10 +6884,14 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6732,10 +6944,14 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -6788,10 +7004,14 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -6844,10 +7064,14 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -6900,10 +7124,14 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6956,10 +7184,14 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -7012,10 +7244,14 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -7068,10 +7304,14 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7124,10 +7364,14 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7180,10 +7424,14 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -7236,10 +7484,14 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7292,10 +7544,14 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -7348,10 +7604,14 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7404,10 +7664,14 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7460,10 +7724,14 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr"/>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -7516,10 +7784,14 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7572,10 +7844,14 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7628,10 +7904,14 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -7684,10 +7964,14 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7740,10 +8024,14 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -7796,10 +8084,14 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7852,10 +8144,14 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr"/>
+          <t>5:5</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -7908,10 +8204,14 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -7964,10 +8264,14 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8020,10 +8324,14 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -8076,10 +8384,14 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8112,7 +8424,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>08-08 23:30</t>
+          <t>08-08 23:40</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -8132,10 +8444,14 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8188,10 +8504,14 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8244,10 +8564,14 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -8300,10 +8624,14 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -8356,10 +8684,14 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8412,10 +8744,14 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -8468,10 +8804,14 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8524,10 +8864,14 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -8580,10 +8924,14 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8636,10 +8984,14 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -8692,10 +9044,14 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
           <t>受球半</t>
@@ -8748,10 +9104,14 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -8804,10 +9164,14 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -8860,10 +9224,14 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8916,10 +9284,14 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -8972,10 +9344,14 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -9028,10 +9404,14 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9084,10 +9464,14 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9140,10 +9524,14 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
           <t>两球</t>
@@ -9196,10 +9584,14 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -9252,10 +9644,14 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9308,10 +9704,14 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -9364,10 +9764,14 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -9420,10 +9824,14 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -9476,10 +9884,14 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9532,10 +9944,14 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -9588,10 +10004,14 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9644,10 +10064,14 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9700,10 +10124,14 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9756,10 +10184,14 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9812,10 +10244,14 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9868,10 +10304,14 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9924,10 +10364,14 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -9980,10 +10424,14 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr"/>
+          <t>1:5</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -10036,10 +10484,14 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -10092,10 +10544,14 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -10148,10 +10604,14 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10204,10 +10664,14 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10260,10 +10724,14 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10316,10 +10784,14 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
           <t>受两球</t>
@@ -10372,10 +10844,14 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10408,7 +10884,7 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>08-09 04:30</t>
+          <t>08-09 04:40</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
@@ -10428,10 +10904,14 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10484,10 +10964,14 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10540,10 +11024,14 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -10596,10 +11084,14 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10652,10 +11144,14 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10708,10 +11204,14 @@
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -10764,10 +11264,14 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10820,10 +11324,14 @@
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -10876,10 +11384,14 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H183" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -12224,10 +12736,14 @@
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr"/>
-      <c r="I207" s="5" t="inlineStr"/>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="J207" s="6" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="K207" s="5" t="inlineStr">
@@ -12237,7 +12753,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26083_dashboard.xlsx
+++ b/docs/data/beidan_26083_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26083期 比赛看板（皇冠历史相同亚盘） — 2026-08-09</t>
+          <t>⚽ 北京单场26083期 比赛看板（皇冠历史相同亚盘） — 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -11444,10 +11444,14 @@
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -11500,10 +11504,14 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H185" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -11556,10 +11564,14 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11612,10 +11624,14 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H187" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -11668,10 +11684,14 @@
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H188" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -11724,10 +11744,14 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -11780,10 +11804,14 @@
       </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H190" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -11836,10 +11864,14 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -11892,10 +11924,14 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H192" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -11948,10 +11984,14 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H193" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -12004,10 +12044,14 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -12040,7 +12084,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>08-09 19:30</t>
+          <t>08-09 19:40</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
@@ -12060,10 +12104,14 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H195" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -12116,10 +12164,14 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr"/>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -12172,10 +12224,14 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -12228,10 +12284,14 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -12284,10 +12344,14 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I199" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -12340,10 +12404,14 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr"/>
+          <t>5:4</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -12396,10 +12464,14 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H201" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12452,10 +12524,14 @@
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -12508,10 +12584,14 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I203" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -12564,10 +12644,14 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12620,10 +12704,14 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H205" s="5" t="inlineStr"/>
+          <t>1:5</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -12676,10 +12764,14 @@
       </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H206" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12732,10 +12824,14 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H207" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I207" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12788,10 +12884,14 @@
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H208" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -12844,10 +12944,14 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H209" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I209" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -12900,10 +13004,14 @@
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H210" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -12956,10 +13064,14 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H211" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -13012,10 +13124,14 @@
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -13068,10 +13184,14 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13124,10 +13244,14 @@
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H214" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13180,10 +13304,14 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H215" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I215" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -13236,10 +13364,14 @@
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -13292,10 +13424,14 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -13348,10 +13484,14 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -13404,10 +13544,14 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" s="5" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13460,10 +13604,14 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -13516,10 +13664,14 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I221" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -13572,10 +13724,14 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H222" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -13628,10 +13784,14 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -13684,10 +13844,14 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13740,10 +13904,14 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H225" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -13796,10 +13964,14 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H226" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -13852,10 +14024,14 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H227" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I227" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -13908,10 +14084,14 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H228" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -13964,10 +14144,14 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I229" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14020,10 +14204,14 @@
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H230" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -14076,10 +14264,14 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I231" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -14132,10 +14324,14 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -14188,10 +14384,14 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -14244,10 +14444,14 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I234" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -14300,10 +14504,14 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I235" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -14356,10 +14564,14 @@
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" s="4" t="inlineStr"/>
+          <t>7:2</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -14412,10 +14624,14 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H237" s="5" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I237" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -14468,10 +14684,14 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14524,10 +14744,14 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14580,10 +14804,14 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H240" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I240" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -14636,10 +14864,14 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H241" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -14692,10 +14924,14 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H242" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14748,10 +14984,14 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H243" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I243" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -14804,10 +15044,14 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H244" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -14860,10 +15104,14 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H245" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14916,10 +15164,14 @@
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H246" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I246" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14972,10 +15224,14 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I247" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -15028,10 +15284,14 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H248" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15084,10 +15344,14 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H249" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
           <t>两球</t>
@@ -15140,10 +15404,14 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H250" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -15196,10 +15464,14 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H251" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -15252,10 +15524,14 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -15308,10 +15584,14 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H253" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H253" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -15364,10 +15644,14 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H254" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15420,10 +15704,14 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H255" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15476,10 +15764,14 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H256" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I256" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15532,10 +15824,14 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H257" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15588,10 +15884,14 @@
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H258" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I258" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -15644,10 +15944,14 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H259" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15700,10 +16004,14 @@
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -15756,10 +16064,14 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H261" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H261" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15812,10 +16124,14 @@
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H262" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15868,10 +16184,14 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H263" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I263" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15924,10 +16244,14 @@
       </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15980,10 +16304,14 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H265" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I265" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -16036,10 +16364,14 @@
       </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H266" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I266" s="4" t="inlineStr">
         <is>
           <t>两球/两球半</t>
@@ -16092,10 +16424,14 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I267" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -16148,10 +16484,14 @@
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H268" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I268" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16204,10 +16544,14 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H269" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -16260,10 +16604,14 @@
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H270" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16316,10 +16664,14 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16372,10 +16724,14 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I272" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -16428,10 +16784,14 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -16484,10 +16844,14 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H274" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I274" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16540,10 +16904,14 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
           <t>半球</t>
